--- a/Submit/Results/1/student/cuongnhhe186494/TC1/TC1_Result.xlsx
+++ b/Submit/Results/1/student/cuongnhhe186494/TC1/TC1_Result.xlsx
@@ -16,46 +16,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>StepId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Action</x:t>
+    <x:t>TestCase</x:t>
   </x:si>
   <x:si>
     <x:t>Passed</x:t>
   </x:si>
   <x:si>
-    <x:t>Message</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USER-StartClient-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartClient</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartClient executed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USER-StartServer-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartServer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartServer executed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USER-Input-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Input</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Input executed</x:t>
+    <x:t>EarnedMark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxMark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TC1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -421,17 +397,16 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E4"/>
+  <x:dimension ref="A1:D2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" s="1" customFormat="1">
+    <x:row r="1" spans="1:4" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -444,59 +419,19 @@
       <x:c r="D1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="B2" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="C2" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="b">
+      <x:c r="D2" s="0">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
